--- a/Se_Sp.xlsx
+++ b/Se_Sp.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mumbuamutunga/Library/CloudStorage/Dropbox/Desktop/Sp:Se_Manuscript/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mumbuamutunga/Library/CloudStorage/Dropbox/Desktop/Sp:Se_Analysis/Sp_Se-analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB93A2B7-2518-E241-9DD6-0C12D88B85DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11887C9-1EED-E144-82B7-463143245522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{B72178FB-8AC9-0040-916E-7177EA3259FD}"/>
   </bookViews>
@@ -18,7 +18,6 @@
     <sheet name="Test" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="42">
   <si>
     <t>Positive</t>
   </si>
@@ -617,6 +616,917 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F7A487B-5E8E-1C47-AC10-4189C030E025}">
+  <dimension ref="A1:M20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" style="2"/>
+    <col min="2" max="2" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="30.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="10.83203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="40" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="5">
+        <v>2020</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="6">
+        <v>2</v>
+      </c>
+      <c r="F2" s="6">
+        <v>2</v>
+      </c>
+      <c r="G2" s="6">
+        <v>0</v>
+      </c>
+      <c r="H2" s="6">
+        <v>0</v>
+      </c>
+      <c r="I2" s="6">
+        <v>0</v>
+      </c>
+      <c r="J2" s="6">
+        <v>0</v>
+      </c>
+      <c r="K2" s="6">
+        <v>2</v>
+      </c>
+      <c r="L2" s="6">
+        <v>0</v>
+      </c>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" spans="1:13" ht="20" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="5">
+        <v>2020</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="6">
+        <v>3</v>
+      </c>
+      <c r="F3" s="6">
+        <v>1</v>
+      </c>
+      <c r="G3" s="6">
+        <v>1</v>
+      </c>
+      <c r="H3" s="6">
+        <v>1</v>
+      </c>
+      <c r="I3" s="6">
+        <v>0</v>
+      </c>
+      <c r="J3" s="6">
+        <v>0</v>
+      </c>
+      <c r="K3" s="6">
+        <v>1</v>
+      </c>
+      <c r="L3" s="6">
+        <v>2</v>
+      </c>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" spans="1:13" ht="20" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="5">
+        <v>2020</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="6">
+        <v>2</v>
+      </c>
+      <c r="F4" s="6">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6">
+        <v>2</v>
+      </c>
+      <c r="H4" s="6">
+        <v>0</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <v>0</v>
+      </c>
+      <c r="K4" s="6">
+        <v>0</v>
+      </c>
+      <c r="L4" s="6">
+        <v>2</v>
+      </c>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" spans="1:13" ht="100" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="5">
+        <v>2021</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="6">
+        <v>5</v>
+      </c>
+      <c r="F5" s="6">
+        <v>3</v>
+      </c>
+      <c r="G5" s="6">
+        <v>1</v>
+      </c>
+      <c r="H5" s="6">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6">
+        <v>0</v>
+      </c>
+      <c r="J5" s="6">
+        <v>1</v>
+      </c>
+      <c r="K5" s="6">
+        <v>4</v>
+      </c>
+      <c r="L5" s="6">
+        <v>1</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="20" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="5">
+        <v>2021</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="6">
+        <v>25</v>
+      </c>
+      <c r="F6" s="6">
+        <v>18</v>
+      </c>
+      <c r="G6" s="6">
+        <v>5</v>
+      </c>
+      <c r="H6" s="6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="6">
+        <v>1</v>
+      </c>
+      <c r="J6" s="6">
+        <v>0</v>
+      </c>
+      <c r="K6" s="6">
+        <v>19</v>
+      </c>
+      <c r="L6" s="6">
+        <v>6</v>
+      </c>
+      <c r="M6" s="9"/>
+    </row>
+    <row r="7" spans="1:13" ht="20" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="5">
+        <v>2021</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="6">
+        <v>6</v>
+      </c>
+      <c r="F7" s="6">
+        <v>4</v>
+      </c>
+      <c r="G7" s="6">
+        <v>1</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6">
+        <v>1</v>
+      </c>
+      <c r="J7" s="6">
+        <v>0</v>
+      </c>
+      <c r="K7" s="6">
+        <v>5</v>
+      </c>
+      <c r="L7" s="6">
+        <v>1</v>
+      </c>
+      <c r="M7" s="9"/>
+    </row>
+    <row r="8" spans="1:13" ht="20" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="5">
+        <v>2021</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6">
+        <v>1</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0</v>
+      </c>
+      <c r="J8" s="6">
+        <v>0</v>
+      </c>
+      <c r="K8" s="6">
+        <v>0</v>
+      </c>
+      <c r="L8" s="6">
+        <v>1</v>
+      </c>
+      <c r="M8" s="9"/>
+    </row>
+    <row r="9" spans="1:13" ht="20" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>2021</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6">
+        <v>1</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0</v>
+      </c>
+      <c r="I9" s="6">
+        <v>0</v>
+      </c>
+      <c r="J9" s="6">
+        <v>0</v>
+      </c>
+      <c r="K9" s="6">
+        <v>0</v>
+      </c>
+      <c r="L9" s="6">
+        <v>1</v>
+      </c>
+      <c r="M9" s="9"/>
+    </row>
+    <row r="10" spans="1:13" ht="20" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="5">
+        <v>2021</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="6">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6">
+        <v>1</v>
+      </c>
+      <c r="I10" s="6">
+        <v>0</v>
+      </c>
+      <c r="J10" s="6">
+        <v>0</v>
+      </c>
+      <c r="K10" s="6">
+        <v>1</v>
+      </c>
+      <c r="L10" s="6">
+        <v>0</v>
+      </c>
+      <c r="M10" s="9"/>
+    </row>
+    <row r="11" spans="1:13" ht="80" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="5">
+        <v>2022</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6">
+        <v>1</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0</v>
+      </c>
+      <c r="I11" s="6">
+        <v>0</v>
+      </c>
+      <c r="J11" s="6">
+        <v>0</v>
+      </c>
+      <c r="K11" s="6">
+        <v>1</v>
+      </c>
+      <c r="L11" s="6">
+        <v>0</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="20" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="5">
+        <v>2022</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="6">
+        <v>9</v>
+      </c>
+      <c r="F12" s="6">
+        <v>9</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6">
+        <v>0</v>
+      </c>
+      <c r="I12" s="6">
+        <v>0</v>
+      </c>
+      <c r="J12" s="6">
+        <v>0</v>
+      </c>
+      <c r="K12" s="6">
+        <v>9</v>
+      </c>
+      <c r="L12" s="6">
+        <v>0</v>
+      </c>
+      <c r="M12" s="6"/>
+    </row>
+    <row r="13" spans="1:13" ht="20" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="5">
+        <v>2022</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="6">
+        <v>5</v>
+      </c>
+      <c r="F13" s="6">
+        <v>5</v>
+      </c>
+      <c r="G13" s="6">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6">
+        <v>0</v>
+      </c>
+      <c r="I13" s="6">
+        <v>0</v>
+      </c>
+      <c r="J13" s="6">
+        <v>0</v>
+      </c>
+      <c r="K13" s="6">
+        <v>5</v>
+      </c>
+      <c r="L13" s="6">
+        <v>0</v>
+      </c>
+      <c r="M13" s="6"/>
+    </row>
+    <row r="14" spans="1:13" ht="20" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="5">
+        <v>2022</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="6">
+        <v>1</v>
+      </c>
+      <c r="F14" s="6">
+        <v>1</v>
+      </c>
+      <c r="G14" s="6">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6">
+        <v>0</v>
+      </c>
+      <c r="I14" s="6">
+        <v>0</v>
+      </c>
+      <c r="J14" s="6">
+        <v>0</v>
+      </c>
+      <c r="K14" s="6">
+        <v>1</v>
+      </c>
+      <c r="L14" s="6">
+        <v>0</v>
+      </c>
+      <c r="M14" s="6"/>
+    </row>
+    <row r="15" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="5">
+        <v>2021</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="6">
+        <v>5</v>
+      </c>
+      <c r="F15" s="6">
+        <v>5</v>
+      </c>
+      <c r="G15" s="6">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6">
+        <v>0</v>
+      </c>
+      <c r="I15" s="6">
+        <v>0</v>
+      </c>
+      <c r="J15" s="6">
+        <v>0</v>
+      </c>
+      <c r="K15" s="6">
+        <v>5</v>
+      </c>
+      <c r="L15" s="6">
+        <v>0</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="20" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="5">
+        <v>2021</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="6">
+        <v>13</v>
+      </c>
+      <c r="F16" s="6">
+        <v>10</v>
+      </c>
+      <c r="G16" s="6">
+        <v>2</v>
+      </c>
+      <c r="H16" s="6">
+        <v>1</v>
+      </c>
+      <c r="I16" s="6">
+        <v>0</v>
+      </c>
+      <c r="J16" s="6">
+        <v>0</v>
+      </c>
+      <c r="K16" s="6">
+        <v>10</v>
+      </c>
+      <c r="L16" s="6">
+        <v>3</v>
+      </c>
+      <c r="M16" s="6"/>
+    </row>
+    <row r="17" spans="1:13" ht="20" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="5">
+        <v>2021</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="6">
+        <v>1</v>
+      </c>
+      <c r="F17" s="6">
+        <v>0</v>
+      </c>
+      <c r="G17" s="6">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6">
+        <v>1</v>
+      </c>
+      <c r="I17" s="6">
+        <v>0</v>
+      </c>
+      <c r="J17" s="6">
+        <v>0</v>
+      </c>
+      <c r="K17" s="6">
+        <v>0</v>
+      </c>
+      <c r="L17" s="6">
+        <v>1</v>
+      </c>
+      <c r="M17" s="6"/>
+    </row>
+    <row r="18" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="5">
+        <v>2022</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="6">
+        <v>2</v>
+      </c>
+      <c r="F18" s="6">
+        <v>2</v>
+      </c>
+      <c r="G18" s="6">
+        <v>0</v>
+      </c>
+      <c r="H18" s="6">
+        <v>0</v>
+      </c>
+      <c r="I18" s="6">
+        <v>0</v>
+      </c>
+      <c r="J18" s="6">
+        <v>0</v>
+      </c>
+      <c r="K18" s="6">
+        <v>2</v>
+      </c>
+      <c r="L18" s="6">
+        <v>0</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="20" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="5">
+        <v>2022</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="6">
+        <v>29</v>
+      </c>
+      <c r="F19" s="6">
+        <v>28</v>
+      </c>
+      <c r="G19" s="6">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6">
+        <v>1</v>
+      </c>
+      <c r="I19" s="6">
+        <v>0</v>
+      </c>
+      <c r="J19" s="6">
+        <v>0</v>
+      </c>
+      <c r="K19" s="6">
+        <v>28</v>
+      </c>
+      <c r="L19" s="6">
+        <v>1</v>
+      </c>
+      <c r="M19" s="6"/>
+    </row>
+    <row r="20" spans="1:13" ht="20" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="5">
+        <v>2022</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="6">
+        <v>1</v>
+      </c>
+      <c r="F20" s="6">
+        <v>1</v>
+      </c>
+      <c r="G20" s="6">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6">
+        <v>0</v>
+      </c>
+      <c r="I20" s="6">
+        <v>0</v>
+      </c>
+      <c r="J20" s="6">
+        <v>0</v>
+      </c>
+      <c r="K20" s="6">
+        <v>1</v>
+      </c>
+      <c r="L20" s="6">
+        <v>0</v>
+      </c>
+      <c r="M20" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F038930-83F3-704E-BF47-445ED7A616C1}">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="19" x14ac:dyDescent="0.25">
+      <c r="A1" s="4"/>
+      <c r="B1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="4"/>
+      <c r="G1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="19" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+      <c r="B3" s="3">
+        <v>90</v>
+      </c>
+      <c r="C3" s="3">
+        <v>6</v>
+      </c>
+      <c r="D3" s="13">
+        <f>B3+C3</f>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="13"/>
+      <c r="F4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+      <c r="B5" s="3">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3">
+        <v>14</v>
+      </c>
+      <c r="D5" s="13">
+        <f>B5+C5</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="19" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="14">
+        <f>B3+B5</f>
+        <v>92</v>
+      </c>
+      <c r="C6" s="14">
+        <f>C3+C5</f>
+        <v>20</v>
+      </c>
+      <c r="D6" s="15">
+        <f>SUM(D3:D5)</f>
+        <v>112</v>
+      </c>
+      <c r="G6">
+        <f>SUM(G2:G4)</f>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="19" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+    </row>
+    <row r="8" spans="1:7" ht="19" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G10">
+        <f>B3/D3</f>
+        <v>0.9375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G12">
+        <f>C5/D5</f>
+        <v>0.875</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82E0CAD2-354F-364A-B986-E83148D38036}">
   <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1447,137 +2357,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F038930-83F3-704E-BF47-445ED7A616C1}">
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="4"/>
-      <c r="G1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-      <c r="B3" s="3">
-        <v>90</v>
-      </c>
-      <c r="C3" s="3">
-        <v>6</v>
-      </c>
-      <c r="D3" s="13">
-        <f>B3+C3</f>
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="13"/>
-      <c r="F4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
-      <c r="B5" s="3">
-        <v>2</v>
-      </c>
-      <c r="C5" s="3">
-        <v>14</v>
-      </c>
-      <c r="D5" s="13">
-        <f>B5+C5</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
-      <c r="B6" s="14">
-        <f>B3+B5</f>
-        <v>92</v>
-      </c>
-      <c r="C6" s="14">
-        <f>C3+C5</f>
-        <v>20</v>
-      </c>
-      <c r="D6" s="15">
-        <f>SUM(D3:D5)</f>
-        <v>112</v>
-      </c>
-      <c r="G6">
-        <f>SUM(G2:G4)</f>
-        <v>113</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-    </row>
-    <row r="8" spans="1:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="G10">
-        <f>B3/D3</f>
-        <v>0.9375</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="G12">
-        <f>C5/D5</f>
-        <v>0.875</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82E0CAD2-354F-364A-B986-E83148D38036}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>